--- a/src/test/resources/testdata/TestDataNg.xlsx
+++ b/src/test/resources/testdata/TestDataNg.xlsx
@@ -1,17 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B0B154-F443-4B47-A25D-435353448F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Register" sheetId="1" r:id="rId4"/>
+    <sheet name="Register" sheetId="1" r:id="rId1"/>
+    <sheet name="Arrays_SearchArray" sheetId="2" r:id="rId2"/>
+    <sheet name="Arrays_SquaresOfSortedArray" sheetId="6" r:id="rId3"/>
+    <sheet name="Arrays_FindEvenNum" sheetId="5" r:id="rId4"/>
+    <sheet name="Arrays_MaxConse" sheetId="4" r:id="rId5"/>
+    <sheet name="CodeEditor" sheetId="3" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="50">
   <si>
     <t>TCID</t>
   </si>
@@ -83,34 +108,167 @@
   </si>
   <si>
     <t>password1</t>
+  </si>
+  <si>
+    <t>ValidCode</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>ArrayLink</t>
+  </si>
+  <si>
+    <t>Button</t>
+  </si>
+  <si>
+    <t>def search(input_list, num):
+    if(num in input_list):
+        print("Element Found")
+    else:
+        print("Not Found")
+search([12, 23, 45, 67, 6, 90] , 12)</t>
+  </si>
+  <si>
+    <t>Element Found</t>
+  </si>
+  <si>
+    <t>Search the array</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>def search(input_list, num):
+    if(num in input_list):
+        print("Element Found")
+    else:
+        print("Element Not Found")
+search([12, 23, 45, 67, 6, 90] , 1)</t>
+  </si>
+  <si>
+    <t>Element Not Found</t>
+  </si>
+  <si>
+    <t>def search(input_list, num):</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Submission Successful</t>
+  </si>
+  <si>
+    <t>Submit</t>
+  </si>
+  <si>
+    <t>Error occurred during submission</t>
+  </si>
+  <si>
+    <t>No tests were collected</t>
+  </si>
+  <si>
+    <t>def sortedSquares(nums):
+    squares_list = []
+    for i in range(0, len(nums)):
+        square = nums[i] * nums[i];
+        squares_list.append(square)
+        sorted_squares_list = sorted(squares_list)
+    return sorted_squares_list;
+i = sortedSquares([-7,-3,2,3,11])
+print (i)</t>
+  </si>
+  <si>
+    <t>[4, 9, 9, 49, 121]</t>
+  </si>
+  <si>
+    <t>def sortedSquares(nums):
+    squares_list = []
+    for i in range(0, len(nums)):
+        square = nums[i] * nums[i];
+        squares_list.append(square)
+        sorted_squares_list = sorted(squares_list)
+        print sorted_squares_list;
+    return sorted_squares_list;
+sortedSquares([-7,-3,2,3,11])</t>
+  </si>
+  <si>
+    <t>def findNumbers(nums):
+    c=0
+    for i in nums:
+        j=str(i)
+        x=len(j)
+        if x%2==0:
+            c=c+1
+            print(c)
+    return c</t>
+  </si>
+  <si>
+    <t>def findMaxConsecutiveOnes(nums) :
+    count = 0
+    result = 0
+    for i in range(0, len(nums)):
+        if (nums[i] == 0):
+            count = 0
+        else:
+            count+= 1
+            result = max(result, count)
+            print(result)
+findMaxConsecutiveOnes([1,0,1,1,0,1])</t>
+  </si>
+  <si>
+    <t>1
+1
+2
+2</t>
+  </si>
+  <si>
+    <t>Some Tests failed. Please review code</t>
+  </si>
+  <si>
+    <t>print('Hello,World')</t>
+  </si>
+  <si>
+    <t>Hello,World</t>
+  </si>
+  <si>
+    <t>System.out.println("Hello,World");</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0066CC"/>
       <name val="&quot;Courier New&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -118,7 +276,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -127,45 +285,941 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="13">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E2C3A926-87C0-4FF4-B0FA-6B5205982629}" name="Table5" displayName="Table5" ref="A1:D7" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="31" totalsRowBorderDxfId="29">
+  <autoFilter ref="A1:D7" xr:uid="{E2C3A926-87C0-4FF4-B0FA-6B5205982629}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{A88E9459-5CF3-4680-B8D0-91CF102A1C74}" name="ValidCode" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{B170A64A-7E07-4923-B54E-E26D446BAE65}" name="Output" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{3916E7BA-83D2-48AC-9624-95DC4FBBB6EA}" name="ArrayLink" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{0B96AB76-DE27-41C1-8C7B-E9671A28128B}" name="Button" dataDxfId="25"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{332B78D2-B13E-4CF9-BFF9-8CBDD6655CA5}" name="Table4" displayName="Table4" ref="A1:C3" totalsRowShown="0" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:C3" xr:uid="{332B78D2-B13E-4CF9-BFF9-8CBDD6655CA5}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{4F345C8A-AFDF-4BDC-93E3-7624701795AC}" name="ValidCode" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{2173F069-5779-49BF-A13C-58F4697C19B5}" name="Output" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{9446CF4E-3842-41B6-8025-AAEDBF1E52E5}" name="Button" dataDxfId="19"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E28A545F-4353-46BF-8E57-F031D4369FA2}" name="Table3" displayName="Table3" ref="A1:C3" totalsRowShown="0" dataDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+  <autoFilter ref="A1:C3" xr:uid="{E28A545F-4353-46BF-8E57-F031D4369FA2}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A026E5AC-1271-4A6E-B2E0-DDA63B69D258}" name="ValidCode" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{336C3DCF-FB84-4781-AA2E-B0A50177D03A}" name="Output" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{71F4EDDC-EB85-416B-9372-8190841B8C3F}" name="Button" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{40DBFBC8-1766-4030-9F25-DBEFED9B2F64}" name="Table2" displayName="Table2" ref="A1:C3" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:C3" xr:uid="{40DBFBC8-1766-4030-9F25-DBEFED9B2F64}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{AD73075D-DCC4-4908-9697-437BDA563AA3}" name="ValidCode" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{4D209730-88BE-4BB0-B200-9E2A44BAE771}" name="Output" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{1E102A5B-E73B-46BF-9A26-FB9F67454A0B}" name="Button" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3339D624-767C-4802-BAD8-99B652A090F3}" name="Table1" displayName="Table1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" totalsRowBorderDxfId="2">
+  <autoFilter ref="A1:B4" xr:uid="{3339D624-767C-4802-BAD8-99B652A090F3}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{D1358128-E5F2-485E-BA64-7D000C5AF106}" name="ValidCode" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{3908DAE1-FED4-4678-84C4-6836F5DDA78A}" name="Output" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -355,23 +1409,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.75"/>
-    <col customWidth="1" min="2" max="2" width="15.38"/>
-    <col customWidth="1" min="3" max="3" width="26.5"/>
-    <col customWidth="1" min="4" max="4" width="15.25"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -385,7 +1442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -399,7 +1456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -407,7 +1464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -418,7 +1475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -432,7 +1489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -443,7 +1500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -454,7 +1511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -468,7 +1525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -482,7 +1539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -496,7 +1553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -504,13 +1561,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>1.23456789E8</v>
+        <v>123456789</v>
       </c>
       <c r="D11" s="5">
-        <v>1.23456789E8</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>123456789</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -524,7 +1581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
         <v>8</v>
@@ -537,6 +1594,316 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3742E12-FFD2-495C-9E50-10459D9E2877}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="81">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="81">
+      <c r="A3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="81">
+      <c r="A5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62A455A-DF53-4A9F-9A55-766E97510592}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="60.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="115.5">
+      <c r="A2" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="104.25">
+      <c r="A3" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8DA5B18-016C-4B0B-8CD3-1799CE4292ED}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="104.25">
+      <c r="A2" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="104.25">
+      <c r="A3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DA1A5D-3853-4052-942C-D0B3FDEEB564}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="49.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="127.5">
+      <c r="A2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="370.5">
+      <c r="A3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A608BB0-9D71-4128-B8A2-E124B4A9B12E}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/TestDataNg.xlsx
+++ b/src/test/resources/testdata/TestDataNg.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B0B154-F443-4B47-A25D-435353448F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00993C94-7D95-4099-8553-C89B8700CE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="48">
   <si>
     <t>TCID</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>Output</t>
-  </si>
-  <si>
-    <t>ArrayLink</t>
   </si>
   <si>
     <t>Button</t>
@@ -133,9 +130,6 @@
     <t>Element Found</t>
   </si>
   <si>
-    <t>Search the array</t>
-  </si>
-  <si>
     <t>run</t>
   </si>
   <si>
@@ -163,9 +157,6 @@
   </si>
   <si>
     <t>Error occurred during submission</t>
-  </si>
-  <si>
-    <t>No tests were collected</t>
   </si>
   <si>
     <t>def sortedSquares(nums):
@@ -191,6 +182,9 @@
         print sorted_squares_list;
     return sorted_squares_list;
 sortedSquares([-7,-3,2,3,11])</t>
+  </si>
+  <si>
+    <t>No tests were collected</t>
   </si>
   <si>
     <t>def findNumbers(nums):
@@ -285,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -424,20 +418,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -492,13 +477,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
@@ -981,44 +965,6 @@
     </dxf>
     <dxf>
       <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1159,12 +1105,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E2C3A926-87C0-4FF4-B0FA-6B5205982629}" name="Table5" displayName="Table5" ref="A1:D7" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="31" totalsRowBorderDxfId="29">
-  <autoFilter ref="A1:D7" xr:uid="{E2C3A926-87C0-4FF4-B0FA-6B5205982629}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A88E9459-5CF3-4680-B8D0-91CF102A1C74}" name="ValidCode" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{B170A64A-7E07-4923-B54E-E26D446BAE65}" name="Output" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{3916E7BA-83D2-48AC-9624-95DC4FBBB6EA}" name="ArrayLink" dataDxfId="26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E2C3A926-87C0-4FF4-B0FA-6B5205982629}" name="Table5" displayName="Table5" ref="A1:C7" totalsRowShown="0" headerRowBorderDxfId="29" tableBorderDxfId="30" totalsRowBorderDxfId="28">
+  <autoFilter ref="A1:C7" xr:uid="{E2C3A926-87C0-4FF4-B0FA-6B5205982629}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A88E9459-5CF3-4680-B8D0-91CF102A1C74}" name="ValidCode" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{B170A64A-7E07-4923-B54E-E26D446BAE65}" name="Output" dataDxfId="26"/>
     <tableColumn id="4" xr3:uid="{0B96AB76-DE27-41C1-8C7B-E9671A28128B}" name="Button" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1600,15 +1545,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3742E12-FFD2-495C-9E50-10459D9E2877}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
     <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" s="26" t="s">
         <v>24</v>
       </c>
@@ -1618,90 +1562,69 @@
       <c r="C1" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="29" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="81">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="81">
-      <c r="A2" s="7" t="s">
+      <c r="B2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="25" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="81">
+      <c r="A3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="B3" s="6" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="81">
-      <c r="A3" s="7" t="s">
+      <c r="C3" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C4" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="81">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="7" t="s">
+      <c r="B5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C5" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="81">
-      <c r="A5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="C6" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="7"/>
       <c r="B7" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1714,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62A455A-DF53-4A9F-9A55-766E97510592}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="60.140625" customWidth="1"/>
@@ -1729,30 +1652,39 @@
       <c r="B1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="29" t="s">
-        <v>27</v>
+      <c r="C1" s="28" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="115.5">
       <c r="A2" s="19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="104.25">
       <c r="A3" s="22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1781,27 +1713,27 @@
         <v>25</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="104.25">
       <c r="A2" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="104.25">
       <c r="A3" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1830,29 +1762,29 @@
         <v>25</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="127.5">
       <c r="A2" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="370.5">
       <c r="A3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="C3" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1886,18 +1818,18 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
